--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2020_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2020_atacama.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:09</t>
+    <t xml:space="preserve">2026-09-24 01:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.37</v>
@@ -707,7 +707,7 @@
         <v>-0.23</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.24</v>
@@ -730,7 +730,7 @@
         <v>0.14</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.26</v>
@@ -744,16 +744,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.1</v>
